--- a/app/src/androidTest/java/ru/iteco/fmhandroid/ui/Cases2.xlsx
+++ b/app/src/androidTest/java/ru/iteco/fmhandroid/ui/Cases2.xlsx
@@ -5,16 +5,21 @@
   <sheets>
     <sheet state="hidden" name="Чек лист 2" sheetId="1" r:id="rId4"/>
     <sheet state="hidden" name="Чек лист" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="1" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="2" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="3" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="4" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="5" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="6" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="7" sheetId="9" r:id="rId12"/>
-    <sheet state="visible" name="8" sheetId="10" r:id="rId13"/>
-    <sheet state="visible" name="9" sheetId="11" r:id="rId14"/>
-    <sheet state="visible" name="10" sheetId="12" r:id="rId15"/>
+    <sheet state="visible" name="АВТОТЕСТ 1" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="АВТОТЕСТ 2" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="АВТОТЕСТ 3" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="1" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="2" sheetId="7" r:id="rId10"/>
+    <sheet state="visible" name="3" sheetId="8" r:id="rId11"/>
+    <sheet state="visible" name="4" sheetId="9" r:id="rId12"/>
+    <sheet state="visible" name="6" sheetId="10" r:id="rId13"/>
+    <sheet state="visible" name="7" sheetId="11" r:id="rId14"/>
+    <sheet state="visible" name="9" sheetId="12" r:id="rId15"/>
+    <sheet state="visible" name="10" sheetId="13" r:id="rId16"/>
+    <sheet state="visible" name="11" sheetId="14" r:id="rId17"/>
+    <sheet state="visible" name="12" sheetId="15" r:id="rId18"/>
+    <sheet state="visible" name="5" sheetId="16" r:id="rId19"/>
+    <sheet state="visible" name="8" sheetId="17" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -22,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="288">
   <si>
     <t>Группа проверок/модуль</t>
   </si>
@@ -366,145 +371,40 @@
     <t>Comments (Комментарий)</t>
   </si>
   <si>
-    <t>TC1-01</t>
-  </si>
-  <si>
-    <t>Проект приложения открыт в Android Studio</t>
-  </si>
-  <si>
-    <t>Выбираем приложение Хоспис, выбираем эмулятор с API 29, нажимаем кнопку RUN</t>
-  </si>
-  <si>
-    <t>Приложение установлено</t>
-  </si>
-  <si>
-    <t>TC1-02</t>
-  </si>
-  <si>
-    <t>Удаление приложения с эмулироемого устройства</t>
-  </si>
-  <si>
-    <t>Приложение полностью удаляено</t>
-  </si>
-  <si>
-    <t>TC1-06</t>
-  </si>
-  <si>
-    <t>Навигация между разделами приложения</t>
+    <t>ATC1-01</t>
   </si>
   <si>
     <t>Приложение установлено на эмулироемое устройство, проект приложения открыт в Android Studio, пользователь авторизован.</t>
   </si>
   <si>
-    <t>Переключение между разделами приложени Main - News (All news) - About - Love is all</t>
-  </si>
-  <si>
-    <t>Разделы переключаются, информация обновляется</t>
-  </si>
-  <si>
-    <t>TC1-27</t>
-  </si>
-  <si>
-    <t>Политики конфиденциальности</t>
-  </si>
-  <si>
-    <t>Открыть меню приложения, перейти в раздел "О приложении"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Политики конфиденциальности и пользовательское соглашение </t>
-  </si>
-  <si>
-    <t>TC3-01</t>
-  </si>
-  <si>
-    <t>Приложение установлено на эмулироемое устройство, проект приложения открыт в Android Studio</t>
-  </si>
-  <si>
-    <t>Переходим в настройки девайса, раздел разрешения приложений, выбираем тестируемое приложение</t>
-  </si>
-  <si>
-    <t>В списке разрешений нет доступа к камере/микрофону/галерее</t>
-  </si>
-  <si>
-    <t>TC3-02</t>
-  </si>
-  <si>
-    <t>Визуальная защита поля Пароль</t>
+    <t>Запуск приложения с помощью Android Studio на эмулируемом устройстве</t>
+  </si>
+  <si>
+    <t>Приложение запускается, отображается экрана загрузки Splash Screen</t>
+  </si>
+  <si>
+    <t>ATC1-02</t>
   </si>
   <si>
     <t>Приложение установлено на эмулироемое устройство, проект приложения открыт в Android Studio.</t>
   </si>
   <si>
-    <t>Ввести пароль в поле ввода пароля</t>
-  </si>
-  <si>
-    <t>В поле с вводом пароля данные скрываются астерисками</t>
-  </si>
-  <si>
-    <t>TC7-01</t>
-  </si>
-  <si>
-    <t>Потребление ресурсов приложением (например расход заряда батареи, сетевой траффик)</t>
-  </si>
-  <si>
-    <t>Активная работа в приложении, чтение и публикация новостей</t>
-  </si>
-  <si>
-    <t>Незначительный расход сетевого трафика и батареи при работе с приложением</t>
-  </si>
-  <si>
-    <t>TC7-02</t>
-  </si>
-  <si>
-    <t>Раздел Тематические Цитаты</t>
-  </si>
-  <si>
-    <t>Список тематических цитат</t>
-  </si>
-  <si>
-    <t>TC7-03</t>
-  </si>
-  <si>
-    <t>Раздел Главная</t>
-  </si>
-  <si>
-    <t>Первая страница приложения</t>
-  </si>
-  <si>
-    <t>Список из 3 только опубликованных новостей</t>
-  </si>
-  <si>
-    <t>TC7-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Переключение между разделами меню приложеня </t>
-  </si>
-  <si>
-    <t>TC1-03</t>
-  </si>
-  <si>
-    <t>Запуск приложения с помощью Android Studio на эмулируемом устройстве</t>
-  </si>
-  <si>
-    <t>Приложение запускается, отображается экрана загрузки Splash Screen</t>
-  </si>
-  <si>
-    <t>TC1-04</t>
-  </si>
-  <si>
     <t>Вводим данные зарегистрированного пользователя в поле логин и пароль, нажимаем кнопу войти</t>
   </si>
   <si>
     <t>Приложение запускается, открывается личный кабинет пользователя</t>
   </si>
   <si>
-    <t>TC1-05</t>
+    <t>ATC1-03</t>
   </si>
   <si>
     <t>Вводим данные незарегистрированного пользователя в поле логин и пароль, нажимаем кнопу войти</t>
   </si>
   <si>
     <t>Приложение не запускается, личный кабинет пользователя неоткрывается</t>
+  </si>
+  <si>
+    <t>ATC1-04</t>
   </si>
   <si>
     <t>Вводим данные на Латинице, Кириллице, а также различные символы в поле логин и пароль зарегистрированного пользователя, нажимаем кнопу войти</t>
@@ -517,7 +417,7 @@
     <t>Отсутствие валидации полей потенциальный риск для инъекций</t>
   </si>
   <si>
-    <t>TC1-07</t>
+    <t>ATC1-05</t>
   </si>
   <si>
     <t>Вводим Логин зарегистрированного пользователя и данные на Латинице, Кириллице, а также различные символы в поле пароль, нажимаем кнопу войти</t>
@@ -527,7 +427,7 @@
 Приложение не запускается, личный кабинет пользователя неоткрывается.</t>
   </si>
   <si>
-    <t>TC1-08</t>
+    <t>ATC1-06</t>
   </si>
   <si>
     <t>Вводим SQL инъекции в поле Логин и Пароль зарегистрированного пользователя, нажимаем кнопу войти</t>
@@ -539,13 +439,25 @@
     <t>Для проверки использованы самые популярные проверки с введение одинарной и двойной кавычки, 'SELECT id, login, email, param1 FROM users WHERE id = ' . addslashes($_GET['id']);' и " OR 1=1; --</t>
   </si>
   <si>
-    <t>TC1-09</t>
+    <t>ATC1-07</t>
   </si>
   <si>
     <t>Вводим Логин зарегистрированного пользователя и SQL инъекции в поле Пароль</t>
   </si>
   <si>
-    <t>TC1-10</t>
+    <t>ATC1-08</t>
+  </si>
+  <si>
+    <t>Визуальная защита поля Пароль</t>
+  </si>
+  <si>
+    <t>Ввести пароль в поле ввода пароля</t>
+  </si>
+  <si>
+    <t>В поле с вводом пароля данные скрываются астерисками</t>
+  </si>
+  <si>
+    <t>ATC2-01</t>
   </si>
   <si>
     <t>Добавление объявления в новостной раздел</t>
@@ -557,6 +469,9 @@
     <t>Раздел News дополнен новым объявлением</t>
   </si>
   <si>
+    <t>ATC2-02</t>
+  </si>
+  <si>
     <t>Добавление объявления в новостной раздел с будущим сроком публикации</t>
   </si>
   <si>
@@ -566,6 +481,9 @@
     <t>Раздел Control Panel дополнен новым объявлением с будущей датой публикации, ожидающим публикации</t>
   </si>
   <si>
+    <t>ATC2-03</t>
+  </si>
+  <si>
     <t>Добавление объявления в новостной раздел с прошедшим сроком публикации</t>
   </si>
   <si>
@@ -575,6 +493,9 @@
     <t xml:space="preserve">Поле "Дата публикации" не позволяет поставить дату публикации раньше текущей даты </t>
   </si>
   <si>
+    <t>ATC2-04</t>
+  </si>
+  <si>
     <t>Добавление объявления в новостной раздел заполненного не полностью</t>
   </si>
   <si>
@@ -584,7 +505,7 @@
     <t>Возникает ошибка не заполнены обязательные поля, раздел News не содержит новое объявление</t>
   </si>
   <si>
-    <t>TC1-11</t>
+    <t>ATC2-05</t>
   </si>
   <si>
     <t>Редактирование объявления из новостного радела</t>
@@ -599,7 +520,7 @@
     <t>В разделе News отображается ранее опубликованное объявление с отредактированными данными</t>
   </si>
   <si>
-    <t>TC1-12</t>
+    <t>ATC2-06</t>
   </si>
   <si>
     <t>Изменение статуса ранее опубликованного объявления</t>
@@ -611,7 +532,7 @@
     <t>В разделе News не отображается ранее опубликованное объявление</t>
   </si>
   <si>
-    <t>TC1-13</t>
+    <t>ATC2-07</t>
   </si>
   <si>
     <t>Удаление объявления из новостного радела</t>
@@ -623,7 +544,7 @@
     <t xml:space="preserve">Объявление удалено  </t>
   </si>
   <si>
-    <t>TC1-14</t>
+    <t>ATC2-08</t>
   </si>
   <si>
     <t>Приложение установлено на эмулироемое устройство, проект приложения открыт в Android Studio, пользователь авторизован, раздел News содержит более 1го опубликованного объявления</t>
@@ -635,7 +556,7 @@
     <t>Объявления отсортированы по дате публикации</t>
   </si>
   <si>
-    <t>TC1-15</t>
+    <t>ATC2-09</t>
   </si>
   <si>
     <t>Отмена всех фильтров</t>
@@ -647,7 +568,7 @@
     <t>В разделе News отображаются все опубликованные объявления</t>
   </si>
   <si>
-    <t>TC1-16</t>
+    <t>ATC2-10</t>
   </si>
   <si>
     <t>Фильтрация новостей по категории и периоду публикации</t>
@@ -659,7 +580,7 @@
     <t>В разделе News отображаются все опубликованные объявления из указанной категории за выбранный период</t>
   </si>
   <si>
-    <t>TC1-17</t>
+    <t>ATC2-11</t>
   </si>
   <si>
     <t>Фильтрация новостей по категории и дате публикации</t>
@@ -671,7 +592,7 @@
     <t>В разделе News отображаются все опубликованные объявления из указанной категории за выбранную дату</t>
   </si>
   <si>
-    <t>TC1-18</t>
+    <t>ATC2-12</t>
   </si>
   <si>
     <t>Фильтрация новостей по категории</t>
@@ -683,7 +604,7 @@
     <t>В разделе News отображаются все опубликованные объявления из указанной категории</t>
   </si>
   <si>
-    <t>TC1-19</t>
+    <t>ATC2-13</t>
   </si>
   <si>
     <t>Фильтрация новостей по дате публикации</t>
@@ -695,7 +616,7 @@
     <t>В разделе News отображаются все опубликованные объявления за выбранную дату</t>
   </si>
   <si>
-    <t>TC1-20</t>
+    <t>ATC2-14</t>
   </si>
   <si>
     <t>Фильтрация новостей за указанный период</t>
@@ -707,7 +628,7 @@
     <t>В разделе News отображаются все опубликованные объявления за выбранный период</t>
   </si>
   <si>
-    <t>TC1-22</t>
+    <t>ATC2-15</t>
   </si>
   <si>
     <t>Скролл элементов</t>
@@ -716,22 +637,73 @@
     <t xml:space="preserve">Перейти в раздел News, использовать вертикальную прокрутку для отображения всех объявлений опубликованных в разделе </t>
   </si>
   <si>
-    <t>Светлая тема установлена по умолчанию</t>
-  </si>
-  <si>
-    <t>Все элементы приложения видимы, цвет фона - светлый, текст черный</t>
-  </si>
-  <si>
-    <t>Переходим в настройки эмулируемого девайса, далее Экран переключаем девайс на темную тему</t>
-  </si>
-  <si>
-    <t>Черный текст на белом фоне станет белым текстом на черном фоне.</t>
-  </si>
-  <si>
-    <t>Инверсия цветов не работает, фон приложения по прежнему светлый, темным окрашены новости и выпадающие списки, цвет текста изменен с черного на белый и еле заметен на бежевом фоне</t>
-  </si>
-  <si>
-    <t>TC1-25</t>
+    <t>АTC3-01</t>
+  </si>
+  <si>
+    <t>Навигация между разделами приложения</t>
+  </si>
+  <si>
+    <t>Переключение между разделами приложени Main - News (All news) - About - Love is all</t>
+  </si>
+  <si>
+    <t>Разделы переключаются, отображаются заголовки экранов</t>
+  </si>
+  <si>
+    <t>TC1-01</t>
+  </si>
+  <si>
+    <t>Проект приложения открыт в Android Studio</t>
+  </si>
+  <si>
+    <t>Выбираем приложение Хоспис, выбираем эмулятор с API 29, нажимаем кнопку RUN</t>
+  </si>
+  <si>
+    <t>Приложение установлено</t>
+  </si>
+  <si>
+    <t>TC1-02</t>
+  </si>
+  <si>
+    <t>Удаление приложения с эмулироемого устройства</t>
+  </si>
+  <si>
+    <t>Приложение полностью удаляено</t>
+  </si>
+  <si>
+    <t>TC2-01</t>
+  </si>
+  <si>
+    <t>Приложение установлено на эмулироемое устройство, проект приложения открыт в Android Studio</t>
+  </si>
+  <si>
+    <t>Переходим в настройки девайса, раздел разрешения приложений, выбираем тестируемое приложение</t>
+  </si>
+  <si>
+    <t>В списке разрешений нет доступа к камере/микрофону/галерее и не запрашивается при использовании приложения</t>
+  </si>
+  <si>
+    <t>TC3-01</t>
+  </si>
+  <si>
+    <t>Раздел "Тематические Цитаты"</t>
+  </si>
+  <si>
+    <t>Список тематических цитат</t>
+  </si>
+  <si>
+    <t>TC4-01</t>
+  </si>
+  <si>
+    <t>Раздел "Главная"</t>
+  </si>
+  <si>
+    <t>Первая (главная) страница приложения</t>
+  </si>
+  <si>
+    <t>Отображение заголовка, списка из 3-4 последних опубликованных новостей и ссылка для перехода в раздел News</t>
+  </si>
+  <si>
+    <t>TC6-01</t>
   </si>
   <si>
     <t>Ориентация экрана (альбомная/портретная)</t>
@@ -743,7 +715,7 @@
     <t>Все элементы приложения при повороте экрана отброжаются верно, сохраняют масштаб, находятся в пределах экрана и продолжают функционировать</t>
   </si>
   <si>
-    <t>TC5-01</t>
+    <t>TC7-01</t>
   </si>
   <si>
     <t>Установить приложение на несколько устройств с различным разрешением экрана</t>
@@ -752,7 +724,7 @@
     <t>Все элементы приложения на разных диагоналях экрана отброжаются верно, сохраняют масштаб, находятся в пределах экрана и продолжают функционировать</t>
   </si>
   <si>
-    <t>TC5-03</t>
+    <t>TC7-02</t>
   </si>
   <si>
     <t>Неактивные элементы</t>
@@ -762,7 +734,7 @@
 2. Открыть меню приложения на главном экране, перейти в раздел Новости, снова открыть меню переход в раздел "О приложении" недоступен</t>
   </si>
   <si>
-    <t>TC5-04</t>
+    <t>TC7-03</t>
   </si>
   <si>
     <t>Отображение заголовков экранов</t>
@@ -774,7 +746,7 @@
     <t>Отображение заголовков экранов при переключении между разделами приложений</t>
   </si>
   <si>
-    <t>TC5-05</t>
+    <t>TC7-04</t>
   </si>
   <si>
     <t>Открыть меню приложения на главном экране, перейти в раздел Новости, нажать кнопку редактировать, нажать системную кнопку назад для перехода в раздел "Новости", нажать системную кнопку назад для перехода в раздел "Главная".</t>
@@ -783,7 +755,98 @@
     <t>Возврат на предыдущий экран</t>
   </si>
   <si>
-    <t>TC1-21</t>
+    <t>TC9-01</t>
+  </si>
+  <si>
+    <t>Сворачивание/разворачивание приложения</t>
+  </si>
+  <si>
+    <t>Свернуть и развернуть приложение с помощью системной кнопки</t>
+  </si>
+  <si>
+    <t>Приложение свернулось, развернулось и продолжило работать с того экрана на котором было свернуто</t>
+  </si>
+  <si>
+    <t>Свернуть приложение с помощью системной кнопки</t>
+  </si>
+  <si>
+    <t>Приложение продолжает работать с того экрана на котором было свернуто в фон</t>
+  </si>
+  <si>
+    <t>TC10-1</t>
+  </si>
+  <si>
+    <t>Разные типы подключений (сотовая связь/Wi-Fi)</t>
+  </si>
+  <si>
+    <t>Переключить сотовую связь на Wi-Fi и обратно.</t>
+  </si>
+  <si>
+    <t>Приложение продолжает работать вне зависимости от типа связи</t>
+  </si>
+  <si>
+    <t>TC10-2</t>
+  </si>
+  <si>
+    <t>Прерывания (входящий звонок/смс/push/будильник/режим «Не беспокоить» и т.д.)</t>
+  </si>
+  <si>
+    <t>Эмулировать входящий вызов с помощью функционала Android Studio / установить будильник на эмуляторе или на реальном устройстве</t>
+  </si>
+  <si>
+    <t>Продолжение работы приложения с того экрана на котором было прервано звонком или сигналом будильника</t>
+  </si>
+  <si>
+    <t>TC10-3</t>
+  </si>
+  <si>
+    <t>1.Переходим в настройки эмулируемого девайса, далее сеть, тип сети перекбчаем на EDGE, устанавливаем уровень сигнала POOR
+2. Перейти в раздел News, нажать кнопку редактировать, нажать кнопку добавить, выбрать категорию объявления, указать название и содержание объявления, выбрать время и дату публикации, нажать сохранить.</t>
+  </si>
+  <si>
+    <t>Объявление опубликовано при низкой пропускной способности сети</t>
+  </si>
+  <si>
+    <t>TC11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Переключение между разделами меню приложеня </t>
+  </si>
+  <si>
+    <t>TC12-02</t>
+  </si>
+  <si>
+    <t>Потребление ресурсов приложением (например расход заряда батареи, сетевой траффик)</t>
+  </si>
+  <si>
+    <t>Активная работа в приложении, чтение и публикация новостей</t>
+  </si>
+  <si>
+    <t>Незначительный расход сетевого трафика 3,67Мб за период с 1.09.2024 по 27.09.2024 и батареи при работе с приложением</t>
+  </si>
+  <si>
+    <t>TC5-01</t>
+  </si>
+  <si>
+    <t>Светлая тема установлена по умолчанию</t>
+  </si>
+  <si>
+    <t>Все элементы приложения видимы, цвет фона - светлый, текст черный</t>
+  </si>
+  <si>
+    <t>TC5-02</t>
+  </si>
+  <si>
+    <t>Переходим в настройки эмулируемого девайса, далее Экран переключаем девайс на темную тему</t>
+  </si>
+  <si>
+    <t>Черный текст на белом фоне станет белым текстом на черном фоне.</t>
+  </si>
+  <si>
+    <t>Инверсия цветов не работает, фон приложения по прежнему светлый, темным окрашены новости и выпадающие списки, цвет текста изменен с черного на белый и еле заметен на бежевом фоне</t>
+  </si>
+  <si>
+    <t>TC8-01</t>
   </si>
   <si>
     <t>Отображение ошибок</t>
@@ -795,7 +858,7 @@
     <t>Появляется всплывающее модульное окно с текстом ошибки</t>
   </si>
   <si>
-    <t>TC4-01</t>
+    <t>TC8-02</t>
   </si>
   <si>
     <t>Смена системного языка</t>
@@ -810,10 +873,10 @@
     <t>Текст цитат из раздела Тематические цитаты не переведены на системный язык</t>
   </si>
   <si>
-    <t>TC4-02</t>
-  </si>
-  <si>
-    <t>Проверка локализации и глобализации</t>
+    <t>TC8-03</t>
+  </si>
+  <si>
+    <t>Формат даты создания и публикации извещения</t>
   </si>
   <si>
     <t>Формат даты создания и публикации извещения (ГОД — МЕСЯЦ — ДЕНЬ или ДЕНЬ — МЕСЯЦ — ГОД.)</t>
@@ -822,7 +885,7 @@
     <t>Год даты создания объявления отображается неверно</t>
   </si>
   <si>
-    <t>TC4-03</t>
+    <t>TC8-04</t>
   </si>
   <si>
     <t>Изменение времени эмулятора</t>
@@ -833,61 +896,6 @@
   </si>
   <si>
     <t>Отображение времени в приложении зависимости от часового пояса</t>
-  </si>
-  <si>
-    <t>TC1-23</t>
-  </si>
-  <si>
-    <t>Сворачивание/разворачивание приложения</t>
-  </si>
-  <si>
-    <t>Свернуть и развернуть приложение с помощью системной кнопки</t>
-  </si>
-  <si>
-    <t>Приложение свернулось, развернулось и продолжило работать с того экрана на котором было свернуто</t>
-  </si>
-  <si>
-    <t>TC1-26</t>
-  </si>
-  <si>
-    <t>Свернуть приложение с помощью системной кнопки</t>
-  </si>
-  <si>
-    <t>Приложение продолжает работать с того экрана на котором было свернуто в фон</t>
-  </si>
-  <si>
-    <t>TC1-24</t>
-  </si>
-  <si>
-    <t>Разные типы подключений (сотовая связь/Wi-Fi)</t>
-  </si>
-  <si>
-    <t>Переключить сотовую связь на Wi-Fi и обратно.</t>
-  </si>
-  <si>
-    <t>Приложение продолжает работать вне зависимости от типа связи</t>
-  </si>
-  <si>
-    <t>TC2-01</t>
-  </si>
-  <si>
-    <t>Прерывания (входящий звонок/смс/push/будильник/режим «Не беспокоить» и т.д.)</t>
-  </si>
-  <si>
-    <t>Эмулировать входящий вызов с помощью функционала Android Studio / установить будильник на эмуляторе или на реальном устройстве</t>
-  </si>
-  <si>
-    <t>Продолжение работы приложения с того экрана на котором было прервано звонком или сигналом будильника</t>
-  </si>
-  <si>
-    <t>TC6-01</t>
-  </si>
-  <si>
-    <t>1.Переходим в настройки эмулируемого девайса, далее сеть, тип сети перекбчаем на EDGE, устанавливаем уровень сигнала POOR
-2. Перейти в раздел News, нажать кнопку редактировать, нажать кнопку добавить, выбрать категорию объявления, указать название и содержание объявления, выбрать время и дату публикации, нажать сохранить.</t>
-  </si>
-  <si>
-    <t>Объявление опубликовано при низкой пропускной способности сети</t>
   </si>
 </sst>
 </file>
@@ -1085,7 +1093,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1207,31 +1215,27 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1239,17 +1243,27 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1272,6 +1286,26 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -5294,29 +5328,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="B2" s="50">
-        <f>ROW(B2)</f>
-        <v>2</v>
-      </c>
-      <c r="C2" s="52" t="s">
-        <v>253</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="F2" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="G2" s="53" t="s">
+      <c r="A2" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>226</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="54"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -5335,136 +5368,6 @@
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="50" t="s">
-        <v>256</v>
-      </c>
-      <c r="B3" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>257</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>259</v>
-      </c>
-      <c r="G3" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="52" t="s">
-        <v>260</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="B4" s="50">
-        <v>2.0</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>262</v>
-      </c>
-      <c r="D4" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="52" t="s">
-        <v>263</v>
-      </c>
-      <c r="G4" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="52" t="s">
-        <v>264</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="50" t="s">
-        <v>265</v>
-      </c>
-      <c r="B5" s="50">
-        <v>3.0</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>266</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>267</v>
-      </c>
-      <c r="F5" s="52" t="s">
-        <v>268</v>
-      </c>
-      <c r="G5" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5514,29 +5417,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="s">
-        <v>269</v>
-      </c>
-      <c r="B2" s="50">
-        <f t="shared" ref="B2:B3" si="1">ROW(B2)</f>
-        <v>2</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>270</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>271</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>272</v>
-      </c>
-      <c r="G2" s="53" t="s">
+      <c r="A2" s="49" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="57">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="G2" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="54"/>
+      <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -5557,29 +5459,28 @@
       <c r="Z2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="s">
-        <v>273</v>
-      </c>
-      <c r="B3" s="50">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>274</v>
-      </c>
-      <c r="F3" s="51" t="s">
-        <v>275</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="A3" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="49">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="54"/>
+      <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
@@ -5598,6 +5499,90 @@
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" s="49">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="49" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="49">
+        <v>4.0</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>239</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5647,29 +5632,28 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="s">
-        <v>276</v>
-      </c>
-      <c r="B2" s="50">
-        <f t="shared" ref="B2:B3" si="1">ROW(B2)</f>
-        <v>2</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>277</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>278</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="G2" s="53" t="s">
+      <c r="A2" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>242</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>243</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>244</v>
+      </c>
+      <c r="G2" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="54"/>
+      <c r="H2" s="52"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -5690,26 +5674,156 @@
       <c r="Z2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="s">
-        <v>280</v>
-      </c>
-      <c r="B3" s="50">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="C3" s="52" t="s">
-        <v>281</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>282</v>
-      </c>
-      <c r="F3" s="51" t="s">
-        <v>283</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="A3" s="49" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="49">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>245</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="52"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="6.25"/>
+    <col customWidth="1" min="3" max="3" width="28.0"/>
+    <col customWidth="1" min="4" max="4" width="41.25"/>
+    <col customWidth="1" min="5" max="5" width="28.38"/>
+    <col customWidth="1" min="6" max="6" width="26.38"/>
+    <col customWidth="1" min="8" max="8" width="20.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="s">
+        <v>247</v>
+      </c>
+      <c r="B2" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="52"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="B3" s="49">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>252</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="F3" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" s="51" t="s">
         <v>50</v>
       </c>
       <c r="H3" s="7"/>
@@ -5733,25 +5847,25 @@
       <c r="Z3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="s">
-        <v>284</v>
-      </c>
-      <c r="B4" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="C4" s="52" t="s">
+      <c r="A4" s="49" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="49">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>285</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="G4" s="53" t="s">
+      <c r="D4" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>256</v>
+      </c>
+      <c r="F4" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="G4" s="51" t="s">
         <v>50</v>
       </c>
       <c r="H4" s="7"/>
@@ -5773,6 +5887,498 @@
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="6.25"/>
+    <col customWidth="1" min="3" max="3" width="28.0"/>
+    <col customWidth="1" min="4" max="4" width="41.25"/>
+    <col customWidth="1" min="5" max="5" width="28.38"/>
+    <col customWidth="1" min="6" max="6" width="26.38"/>
+    <col customWidth="1" min="8" max="8" width="20.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" s="56">
+        <v>8.0</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="6.25"/>
+    <col customWidth="1" min="3" max="3" width="28.0"/>
+    <col customWidth="1" min="4" max="4" width="41.25"/>
+    <col customWidth="1" min="5" max="5" width="28.38"/>
+    <col customWidth="1" min="6" max="6" width="26.38"/>
+    <col customWidth="1" min="8" max="8" width="20.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="43">
+        <v>2.0</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>263</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="6.25"/>
+    <col customWidth="1" min="3" max="3" width="28.0"/>
+    <col customWidth="1" min="4" max="4" width="41.25"/>
+    <col customWidth="1" min="5" max="5" width="28.38"/>
+    <col customWidth="1" min="6" max="6" width="26.38"/>
+    <col customWidth="1" min="8" max="8" width="20.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="s">
+        <v>264</v>
+      </c>
+      <c r="B2" s="58">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="57"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="B3" s="58">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>269</v>
+      </c>
+      <c r="G3" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="6.25"/>
+    <col customWidth="1" min="3" max="3" width="28.0"/>
+    <col customWidth="1" min="4" max="4" width="41.25"/>
+    <col customWidth="1" min="5" max="5" width="28.38"/>
+    <col customWidth="1" min="6" max="6" width="26.38"/>
+    <col customWidth="1" min="8" max="8" width="20.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1" s="42" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="49" t="s">
+        <v>271</v>
+      </c>
+      <c r="B2" s="49">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="53" t="s">
+        <v>274</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="52"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="49" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="49">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>276</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="G3" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="53" t="s">
+        <v>279</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="B4" s="49">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="60" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="53" t="s">
+        <v>283</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="49" t="s">
+        <v>284</v>
+      </c>
+      <c r="B5" s="49">
+        <v>4.0</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="G5" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -13740,7 +14346,7 @@
     <col customWidth="1" min="4" max="4" width="41.25"/>
     <col customWidth="1" min="5" max="5" width="28.38"/>
     <col customWidth="1" min="6" max="6" width="26.38"/>
-    <col customWidth="1" min="8" max="8" width="14.63"/>
+    <col customWidth="1" min="8" max="8" width="20.13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13774,50 +14380,206 @@
         <v>114</v>
       </c>
       <c r="B2" s="43">
-        <f t="shared" ref="B2:B3" si="1">ROW(B1:B2)</f>
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="44" t="s">
         <v>116</v>
       </c>
       <c r="F2" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="43"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3">
       <c r="A3" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="B3" s="43">
+      <c r="B3" s="46">
+        <f t="shared" ref="B3:B9" si="1">ROW(B2:B3)</f>
+        <v>2</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>120</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="46"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="46">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="45" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="44" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="47" t="s">
+      <c r="E4" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="G4" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="43"/>
+      <c r="H4" s="46"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="46">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="46">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" s="46">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="46">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B9" s="46">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -13837,7 +14599,7 @@
     <col customWidth="1" min="4" max="4" width="41.25"/>
     <col customWidth="1" min="5" max="5" width="28.38"/>
     <col customWidth="1" min="6" max="6" width="26.38"/>
-    <col customWidth="1" min="8" max="8" width="20.13"/>
+    <col customWidth="1" min="8" max="8" width="14.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13867,52 +14629,70 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="s">
-        <v>121</v>
+      <c r="A2" s="49" t="s">
+        <v>142</v>
       </c>
       <c r="B2" s="49">
         <v>1.0</v>
       </c>
-      <c r="C2" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="G2" s="47" t="s">
+      <c r="C2" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="G2" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="4"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="s">
-        <v>126</v>
+      <c r="A3" s="49" t="s">
+        <v>146</v>
       </c>
       <c r="B3" s="49">
         <v>2.0</v>
       </c>
-      <c r="C3" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>129</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="C3" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="53" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="54"/>
+      <c r="H3" s="52"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
@@ -13933,51 +14713,70 @@
       <c r="Z3" s="7"/>
     </row>
     <row r="4">
-      <c r="A4" s="43" t="s">
-        <v>130</v>
+      <c r="A4" s="49" t="s">
+        <v>150</v>
       </c>
       <c r="B4" s="49">
         <v>3.0</v>
       </c>
-      <c r="C4" s="46" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4" s="53" t="s">
+      <c r="C4" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E4" s="53" t="s">
+        <v>152</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="G4" s="51" t="s">
         <v>50</v>
       </c>
+      <c r="H4" s="52"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
+      <c r="V4" s="7"/>
+      <c r="W4" s="7"/>
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7"/>
+      <c r="Z4" s="7"/>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="s">
-        <v>134</v>
+      <c r="A5" s="49" t="s">
+        <v>154</v>
       </c>
       <c r="B5" s="49">
         <v>4.0</v>
       </c>
-      <c r="C5" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="G5" s="53" t="s">
+      <c r="C5" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="52"/>
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
@@ -13998,96 +14797,466 @@
       <c r="Z5" s="7"/>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="s">
-        <v>139</v>
+      <c r="A6" s="49" t="s">
+        <v>158</v>
       </c>
       <c r="B6" s="49">
         <v>5.0</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="G6" s="53" t="s">
+      <c r="C6" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="G6" s="51" t="s">
         <v>50</v>
       </c>
+      <c r="H6" s="52"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="s">
-        <v>143</v>
+      <c r="A7" s="49" t="s">
+        <v>163</v>
       </c>
       <c r="B7" s="49">
         <v>6.0</v>
       </c>
-      <c r="C7" s="55" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="G7" s="53" t="s">
+      <c r="C7" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="G7" s="51" t="s">
         <v>50</v>
       </c>
+      <c r="H7" s="52"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="s">
-        <v>146</v>
+      <c r="A8" s="49" t="s">
+        <v>167</v>
       </c>
       <c r="B8" s="49">
         <v>7.0</v>
       </c>
-      <c r="C8" s="55" t="s">
-        <v>147</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="55" t="s">
-        <v>148</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="G8" s="53" t="s">
+      <c r="C8" s="50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8" s="51" t="s">
         <v>50</v>
       </c>
+      <c r="H8" s="52"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" s="55">
+      <c r="A9" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="49">
         <v>8.0</v>
       </c>
-      <c r="C9" s="56" t="s">
-        <v>94</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="46" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="56" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="53" t="s">
+      <c r="C9" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" s="51" t="s">
         <v>50</v>
       </c>
+      <c r="H9" s="52"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="B10" s="49">
+        <v>9.0</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" s="52"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="49">
+        <v>10.0</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="52"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="49">
+        <v>11.0</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="52"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+      <c r="Y12" s="7"/>
+      <c r="Z12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="49">
+        <v>12.0</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="52"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+      <c r="Y13" s="7"/>
+      <c r="Z13" s="7"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" s="49">
+        <v>13.0</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="G14" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="52"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7"/>
+      <c r="Z14" s="7"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="B15" s="49">
+        <v>14.0</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="52"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7"/>
+      <c r="Z15" s="7"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="B16" s="49">
+        <v>15.0</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="F16" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="G16" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="52"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -14138,209 +15307,27 @@
     </row>
     <row r="2">
       <c r="A2" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="B2" s="49">
+        <v>202</v>
+      </c>
+      <c r="B2" s="43">
         <v>1.0</v>
       </c>
-      <c r="C2" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="45" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" s="47" t="s">
+      <c r="C2" s="44" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="43"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="B3" s="43">
-        <f t="shared" ref="B3:B9" si="1">ROW(B2:B3)</f>
-        <v>2</v>
-      </c>
-      <c r="C3" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="46" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="G3" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="43"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="B4" s="43">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" s="46" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="G4" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="43"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="43">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="46" t="s">
-        <v>162</v>
-      </c>
-      <c r="G5" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="46" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="B6" s="43">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="G6" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="46" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="B7" s="43">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="C7" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="G7" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="46" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="43">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="C8" s="46" t="s">
-        <v>55</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="G8" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="46" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="43" t="s">
-        <v>173</v>
-      </c>
-      <c r="B9" s="43">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="C9" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F9" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="G9" s="47" t="s">
-        <v>50</v>
-      </c>
+      <c r="H2" s="4"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -14390,648 +15377,54 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="57">
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="G2" s="53" t="s">
+      <c r="A2" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="46">
+        <f t="shared" ref="B2:B3" si="1">ROW(B1:B2)</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>208</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>209</v>
+      </c>
+      <c r="G2" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="54"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
+      <c r="H2" s="46"/>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="50">
-        <f t="shared" ref="B3:B15" si="1">ROW(B2:B3)</f>
+      <c r="A3" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="46">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="C3" s="52" t="s">
-        <v>177</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>178</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>179</v>
-      </c>
-      <c r="G3" s="53" t="s">
+      <c r="C3" s="54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="G3" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="54"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="50" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="50">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="F4" s="52" t="s">
-        <v>182</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="50" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="50">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>183</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="G5" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="50" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="50">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>190</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="54"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="B7" s="50">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="D7" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="E7" s="51" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="51" t="s">
-        <v>194</v>
-      </c>
-      <c r="G7" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="54"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="B8" s="50">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>196</v>
-      </c>
-      <c r="D8" s="51" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="51" t="s">
-        <v>197</v>
-      </c>
-      <c r="F8" s="51" t="s">
-        <v>198</v>
-      </c>
-      <c r="G8" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="54"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="50">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="C9" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E9" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="54"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10" s="50">
-        <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E10" s="51" t="s">
-        <v>205</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="G10" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" s="54"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11" s="50">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>209</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>210</v>
-      </c>
-      <c r="G11" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H11" s="54"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="B12" s="50">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>212</v>
-      </c>
-      <c r="D12" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>213</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>214</v>
-      </c>
-      <c r="G12" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="54"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="50">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E13" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="F13" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="G13" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="54"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="50">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="C14" s="52" t="s">
-        <v>220</v>
-      </c>
-      <c r="D14" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E14" s="52" t="s">
-        <v>221</v>
-      </c>
-      <c r="F14" s="52" t="s">
-        <v>222</v>
-      </c>
-      <c r="G14" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="54"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="50" t="s">
-        <v>223</v>
-      </c>
-      <c r="B15" s="50">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="C15" s="52" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E15" s="52" t="s">
-        <v>225</v>
-      </c>
-      <c r="F15" s="52" t="s">
-        <v>226</v>
-      </c>
-      <c r="G15" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="54"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="50" t="s">
-        <v>227</v>
-      </c>
-      <c r="B16" s="50">
-        <f>ROW(B16)</f>
-        <v>16</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>228</v>
-      </c>
-      <c r="D16" s="51" t="s">
-        <v>200</v>
-      </c>
-      <c r="E16" s="51" t="s">
-        <v>229</v>
-      </c>
-      <c r="F16" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="G16" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="54"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
+      <c r="H3" s="46"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -15081,86 +15474,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="F2" s="52" t="s">
-        <v>231</v>
-      </c>
-      <c r="G2" s="53" t="s">
+      <c r="A2" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="43">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="G2" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="50"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>232</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>233</v>
-      </c>
-      <c r="G3" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -15210,46 +15544,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="s">
-        <v>235</v>
-      </c>
-      <c r="B2" s="57">
+      <c r="A2" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="B2" s="43">
         <v>1.0</v>
       </c>
-      <c r="C2" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>238</v>
-      </c>
-      <c r="G2" s="53" t="s">
+      <c r="C2" s="56" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>219</v>
+      </c>
+      <c r="G2" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H2" s="54"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -15267,8 +15582,8 @@
     <col customWidth="1" min="2" max="2" width="6.25"/>
     <col customWidth="1" min="3" max="3" width="28.0"/>
     <col customWidth="1" min="4" max="4" width="41.25"/>
-    <col customWidth="1" min="5" max="5" width="28.38"/>
-    <col customWidth="1" min="6" max="6" width="26.38"/>
+    <col customWidth="1" min="5" max="5" width="32.75"/>
+    <col customWidth="1" min="6" max="6" width="28.75"/>
     <col customWidth="1" min="8" max="8" width="20.13"/>
   </cols>
   <sheetData>
@@ -15298,173 +15613,28 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="50" t="s">
-        <v>239</v>
-      </c>
-      <c r="B3" s="50">
-        <v>1.0</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="F3" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="G3" s="47" t="s">
+    <row r="2">
+      <c r="A2" s="43" t="s">
+        <v>220</v>
+      </c>
+      <c r="B2" s="43">
+        <v>7.0</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>221</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="50" t="s">
-        <v>242</v>
-      </c>
-      <c r="B4" s="57">
-        <v>2.0</v>
-      </c>
-      <c r="C4" s="52" t="s">
-        <v>243</v>
-      </c>
-      <c r="D4" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>244</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="50" t="s">
-        <v>245</v>
-      </c>
-      <c r="B5" s="57">
-        <v>3.0</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>246</v>
-      </c>
-      <c r="D5" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="51" t="s">
-        <v>247</v>
-      </c>
-      <c r="F5" s="52" t="s">
-        <v>248</v>
-      </c>
-      <c r="G5" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="50" t="s">
-        <v>249</v>
-      </c>
-      <c r="B6" s="57">
-        <v>4.0</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="D6" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="F6" s="52" t="s">
-        <v>251</v>
-      </c>
-      <c r="G6" s="47" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
